--- a/search/ipd/ipd_target_candidates.xlsx
+++ b/search/ipd/ipd_target_candidates.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -574,19 +574,26 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>邮箱地址不要写进这张表或仓库：只写通讯作者姓名和‘在哪里找到地址’（论文 / 机构网页 / 其他）。</t>
+          <t>decided_by_screeners 列：已经有两位筛选员全文判断的报告写在这里。2026 年 10 月 19 日 20 篇校准后（作者转告，Claude 没有打开论文核对）：WS1859 有 19 行逐例表，WS0049 的逐例资料在线上附录 1（6 行），两篇都判 Include，不是 IPD 索取对象。它们仍留在表里，只为保留规划时的记录。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>发邮件前仍要先核对全文：确实只有汇总数据、确实是游走脾、确实有儿童（IPD 邮件草稿第 1 节的清单）。</t>
+          <t>邮箱地址不要写进这张表或仓库：只写通讯作者姓名和‘在哪里找到地址’（论文 / 机构网页 / 其他）。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>发邮件前仍要先核对全文：确实只有汇总数据、确实是游走脾、确实有儿童（IPD 邮件草稿第 1 节的清单）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>一次性批量发出；第一封后 4 周发第二封；再等 4 周；从第一封起最多 8 周（D6）。IPD_requests 表（提取工作簿）记录进度。</t>
         </is>
@@ -1221,7 +1228,11 @@
       </c>
       <c r="Q8" s="2" t="inlineStr"/>
       <c r="R8" s="2" t="inlineStr"/>
-      <c r="S8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 calibration: Include - per-patient Table 1 with 19 rows (screeners' report); not an IPD target</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -2010,7 +2021,11 @@
       </c>
       <c r="Q19" s="2" t="inlineStr"/>
       <c r="R19" s="2" t="inlineStr"/>
-      <c r="S19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 calibration: Include - 6-row per-patient table in online appendix 1 (screeners' report); not an IPD target</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
